--- a/backend/eval/planilla_juez_ia.xlsx
+++ b/backend/eval/planilla_juez_ia.xlsx
@@ -6898,7 +6898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6963,25 +6963,22 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Mitradel publico nuevas vacantes de empleo en su portal, segun reporto TVN el 7 de octubre de 2026.</t>
+          <t>TVN publicó con fecha 2026-10-07T21:34:03Z una noticia titulada "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles".</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>[N-6ffd1c40b65f:titulo] "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles"
-[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"</t>
+          <t>[N-6ffd1c40b65f:medio] "TVN"
+[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"
+[N-6ffd1c40b65f:titulo] "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles"</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -6999,25 +6996,22 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>La tasa de desempleo anual en Panama para el ano 2024 fue de 8.451% de la poblacion activa.</t>
+          <t>El dato anual histórico de desempleo registrado por el Banco Mundial para Panamá en el año 2024 fue de 8.451 % de la población activa.</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451
-[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024</t>
+          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024
+[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451
+[WB:PAN:SL.UEM.TOTL.ZS:2024:unidad] "% de la población activa"</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>"de la población activa" sale de la definición del indicador, no de lo citado</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -7030,17 +7024,19 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>afirmación (hecho)</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>En 2023, la tasa de desempleo registrada en Panama fue de 6.544%.</t>
+          <t>El medio TVN [N-6ffd1c40b65f:medio] publicó el 2026-10-07T21:34:03Z [N-6ffd1c40b65f:fecha] un reporte titulado "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles" [N-6ffd1c40b65f:titulo].</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:serie] [{"anio": 2020, "valor": 14.663}, {"anio": 2021, "valor": 10.177}, {"anio": 2022, "valor": 8.086}, {"anio": 2023, "valor": 6.544}, {"anio": 2024, "valor": 8.451}]</t>
+          <t>[N-6ffd1c40b65f:medio] "TVN"
+[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"
+[N-6ffd1c40b65f:titulo] "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles"</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -7066,25 +7062,22 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>El medio TVN publico el 7 de octubre de 2026 [N-6ffd1c40b65f:fecha] que Mitradel habilito nuevas vacantes de empleo en su portal web [N-6ffd1c40b65f:titulo].</t>
+          <t>Como contexto histórico de referencia previa, el indicador anual del Banco Mundial situó el desempleo en Panamá para el año 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio] en 8.451 [WB:PAN:SL.UEM.TOTL.ZS:2024:valor] % de la población activa [WB:PAN:SL.UEM.TOTL.ZS:2024:unidad].</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"
-[N-6ffd1c40b65f:titulo] "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles"</t>
+          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024
+[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451
+[WB:PAN:SL.UEM.TOTL.ZS:2024:unidad] "% de la población activa"</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -7097,32 +7090,27 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>guion_45_60s</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Por otro lado, los datos historicos del Banco Mundial indican que en el ano 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio] la tasa de desempleo en Panama fue de 8.451% [WB:PAN:SL.UEM.TOTL.ZS:2024:valor] de la poblacion activa, mostrando un incremento en comparacion con el 6.544% [WB:PAN:SL.UEM.TOTL.ZS:2024:serie] registrado en el ano 2023 [WB:PAN:SL.UEM.TOTL.ZS:2024:serie].</t>
+          <t>El medio TVN [N-6ffd1c40b65f:medio] publicó el 2026-10-07T21:34:03Z [N-6ffd1c40b65f:fecha] una información titulada "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles" [N-6ffd1c40b65f:titulo].</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024
-[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451
-[WB:PAN:SL.UEM.TOTL.ZS:2024:serie] [{"anio": 2020, "valor": 14.663}, {"anio": 2021, "valor": 10.177}, {"anio": 2022, "valor": 8.086}, {"anio": 2023, "valor": 6.544}, {"anio": 2024, "valor": 8.451}]
-[WB:PAN:SL.UEM.TOTL.ZS:2024:serie] [{"anio": 2020, "valor": 14.663}, {"anio": 2021, "valor": 10.177}, {"anio": 2022, "valor": 8.086}, {"anio": 2023, "valor": 6.544}, {"anio": 2024, "valor": 8.451}]</t>
+          <t>[N-6ffd1c40b65f:medio] "TVN"
+[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"
+[N-6ffd1c40b65f:titulo] "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles"</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>"de la población activa" sale de la definición del indicador, no de lo citado</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -7135,19 +7123,19 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>guion_45_60s</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>En la region, para el ano 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio], Costa Rica registro 6.936% [WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion] y Republica Dominicana 5.312% [WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion].</t>
+          <t>Como antecedente histórico del mercado laboral, el Banco Mundial registró para Panamá en el año 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio] una tasa de desempleo de 8.451 [WB:PAN:SL.UEM.TOTL.ZS:2024:valor] % de la población activa [WB:PAN:SL.UEM.TOTL.ZS:2024:unidad].</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
           <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024
-[WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion] [{"pais": "CRI", "anio": 2024, "valor": 6.936}, {"pais": "DOM", "anio": 2024, "valor": 5.312}]
-[WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion] [{"pais": "CRI", "anio": 2024, "valor": 6.936}, {"pais": "DOM", "anio": 2024, "valor": 5.312}]</t>
+[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451
+[WB:PAN:SL.UEM.TOTL.ZS:2024:unidad] "% de la población activa"</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -7168,30 +7156,27 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>guion_45_60s</t>
+          <t>copy_digital</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>El medio TVN informo el 7 de octubre de 2026 [N-6ffd1c40b65f:fecha] sobre la publicacion de nuevas vacantes de empleo en el portal de Mitradel [N-6ffd1c40b65f:titulo].</t>
+          <t>TVN [N-6ffd1c40b65f:medio] publicó el 2026-10-07T21:34:03Z [N-6ffd1c40b65f:fecha] que el Mitradel habilitó nuevas vacantes laborales en su portal web [N-6ffd1c40b65f:titulo].</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"
+          <t>[N-6ffd1c40b65f:medio] "TVN"
+[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"
 [N-6ffd1c40b65f:titulo] "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles"</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -7204,30 +7189,27 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>guion_45_60s</t>
+          <t>copy_digital</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Esta iniciativa surge en un contexto donde, segun datos historicos del Banco Mundial, la tasa de desempleo en Panama para el ano 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio] se situo en 8.451% [WB:PAN:SL.UEM.TOTL.ZS:2024:valor] de la poblacion activa.</t>
+          <t>Como referencia histórica previa, el Banco Mundial situó el desempleo en Panamá en 8.451 [WB:PAN:SL.UEM.TOTL.ZS:2024:valor] % de la población activa [WB:PAN:SL.UEM.TOTL.ZS:2024:unidad] en el año 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio].</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024
-[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451</t>
+          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451
+[WB:PAN:SL.UEM.TOTL.ZS:2024:unidad] "% de la población activa"
+[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>"de la población activa" sale de la definición del indicador, no de lo citado</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -7235,23 +7217,24 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-6ffd1c40b65f</t>
+          <t>CASO-EV-N-3d58bd578f4b</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>guion_45_60s</t>
+          <t>afirmación (declaracion)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Esta cifra represento un aumento frente al 6.544% [WB:PAN:SL.UEM.TOTL.ZS:2024:serie] reportado en el ano 2023 [WB:PAN:SL.UEM.TOTL.ZS:2024:serie].</t>
+          <t>El medio TVN publico el 8 de octubre de 2026 una noticia cuyo titular indica que mas de 200 universitarios participan en la Hackathon Copa Airlines 2026 en Veraguas.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:serie] [{"anio": 2020, "valor": 14.663}, {"anio": 2021, "valor": 10.177}, {"anio": 2022, "valor": 8.086}, {"anio": 2023, "valor": 6.544}, {"anio": 2024, "valor": 8.451}]
-[WB:PAN:SL.UEM.TOTL.ZS:2024:serie] [{"anio": 2020, "valor": 14.663}, {"anio": 2021, "valor": 10.177}, {"anio": 2022, "valor": 8.086}, {"anio": 2023, "valor": 6.544}, {"anio": 2024, "valor": 8.451}]</t>
+          <t>[N-3d58bd578f4b:medio] "TVN"
+[N-3d58bd578f4b:fecha] "2026-10-08T18:27:29Z"
+[N-3d58bd578f4b:titulo] "Más de 200 universitarios participan en la Hackathon Copa Airlines 2026 en Veraguas"</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -7267,24 +7250,24 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-6ffd1c40b65f</t>
+          <t>CASO-EV-N-1a8d986bf866</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>guion_45_60s</t>
+          <t>afirmación (declaracion)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>En la comparacion regional del ano 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio], Costa Rica registro un desempleo de 6.936% [WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion] y Republica Dominicana un 5.312% [WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion].</t>
+          <t>El titular indica una explosión demográfica en Panamá Este que aumenta la presión sobre el transporte público.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024
-[WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion] [{"pais": "CRI", "anio": 2024, "valor": 6.936}, {"pais": "DOM", "anio": 2024, "valor": 5.312}]
-[WB:PAN:SL.UEM.TOTL.ZS:2024:comparacion] [{"pais": "CRI", "anio": 2024, "valor": 6.936}, {"pais": "DOM", "anio": 2024, "valor": 5.312}]</t>
+          <t>[N-1a8d986bf866:titulo] "Explosión demográfica en Panamá Este aumenta la presión sobre el transporte público"
+[N-1a8d986bf866:medio] "TVN"
+[N-1a8d986bf866:fecha] "2026-10-08T12:55:10Z"</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -7300,35 +7283,32 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-6ffd1c40b65f</t>
+          <t>CASO-EV-N-e2e7ae51395c</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>copy_digital</t>
+          <t>afirmación (declaracion)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Mitradel publica nuevas vacantes de empleo en su portal web, segun reporto TVN el 7 de octubre de 2026 [N-6ffd1c40b65f:fecha] [N-6ffd1c40b65f:titulo].</t>
+          <t>Según TVN, el ITSE se suma a una iniciativa para proyectar el café panameño y formar baristas.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>[N-6ffd1c40b65f:fecha] "2026-10-07T21:34:03Z"
-[N-6ffd1c40b65f:titulo] "Empleos en Panamá: Mitradel publica en su portal nuevas vacantes disponibles"</t>
+          <t>[N-e2e7ae51395c:titulo] "ITSE se suma a iniciativa para proyectar el café panameño y formar baristas"
+[N-e2e7ae51395c:medio] "TVN"
+[N-e2e7ae51395c:fecha] "2026-10-07T22:55:56Z"</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -7336,36 +7316,32 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-6ffd1c40b65f</t>
+          <t>CASO-EV-N-34877dd09e6b</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>copy_digital</t>
+          <t>afirmación (declaracion)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Como contexto historico, la tasa de desempleo en Panama para el ano 2024 [WB:PAN:SL.UEM.TOTL.ZS:2024:anio] fue de 8.451% [WB:PAN:SL.UEM.TOTL.ZS:2024:valor] de la poblacion activa, segun registros del Banco Mundial [WB:PAN:SL.UEM.TOTL.ZS:2024:valor].</t>
+          <t>El FMI proyecta que la economía de Panamá crecerá cerca de 5% en 2026.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>[WB:PAN:SL.UEM.TOTL.ZS:2024:anio] 2024
-[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451
-[WB:PAN:SL.UEM.TOTL.ZS:2024:valor] 8.451</t>
+          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"
+[N-34877dd09e6b:medio] "TVN"
+[N-34877dd09e6b:fecha] "2026-10-07T22:00:00Z"</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>"de la población activa" sale de la definición del indicador, no de lo citado</t>
-        </is>
-      </c>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -7373,7 +7349,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-3d58bd578f4b</t>
+          <t>CASO-EV-N-34877dd09e6b</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -7383,13 +7359,14 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Según un titular publicado por el medio TVN el 8 de octubre de 2026, más de 200 universitarios participan en la Hackathon Copa Airlines 2026 en Veraguas.</t>
+          <t>Un economista explicará el impacto de las tasas de interés en la economía panameña y la posible subida de cuotas de préstamos.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>[N-3d58bd578f4b:titulo] "Más de 200 universitarios participan en la Hackathon Copa Airlines 2026 en Veraguas"
-[N-3d58bd578f4b:fecha] "2026-10-08T18:27:29Z"</t>
+          <t>[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"
+[N-bc0c4a46f2c5:medio] "TVN"
+[N-bc0c4a46f2c5:fecha] "2026-10-08T13:23:50Z"</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -7399,7 +7376,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
+          <t>el titular dice "explica"; la frase lo pasa a futuro ("explicará")</t>
         </is>
       </c>
     </row>
@@ -7409,22 +7386,24 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-33f2663b5f67</t>
+          <t>CASO-EV-N-34877dd09e6b</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>afirmación (declaracion)</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>El titular informa que el MOP avanza en más del 45% una nueva ruta para desahogar la vía Interamericana en David.</t>
+          <t>TVN informó que el FMI proyecta un crecimiento cercano al 5% para la economía de Panamá en 2026 [N-34877dd09e6b:titulo][N-34877dd09e6b:medio][N-34877dd09e6b:fecha].</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>[N-33f2663b5f67:titulo] "MOP avanza en mas del 45% nueva ruta para desahogar la via Interamericana en David"</t>
+          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"
+[N-34877dd09e6b:medio] "TVN"
+[N-34877dd09e6b:fecha] "2026-10-07T22:00:00Z"</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -7440,22 +7419,24 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-7f5a31e89279</t>
+          <t>CASO-EV-N-34877dd09e6b</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>afirmación (declaracion)</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TVN reporta que en Bocas del Toro se están afinando los detalles para el III Simulacro de Evacuación.</t>
+          <t>Además, otro titular indica que un economista explicará cómo las tasas de interés podrían elevar las cuotas de préstamos en el país [N-bc0c4a46f2c5:titulo][N-bc0c4a46f2c5:medio][N-bc0c4a46f2c5:fecha].</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>[N-7f5a31e89279:titulo] "Bocas del Toro afina detalles para el III Simulacro de Evacuación este lunes 12 de octubre"</t>
+          <t>[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"
+[N-bc0c4a46f2c5:medio] "TVN"
+[N-bc0c4a46f2c5:fecha] "2026-10-08T13:23:50Z"</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -7465,7 +7446,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
+          <t>el titular dice "explica"; la frase lo pasa a futuro ("explicará")</t>
         </is>
       </c>
     </row>
@@ -7475,30 +7456,35 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-7f5a31e89279</t>
+          <t>CASO-EV-N-34877dd09e6b</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>afirmación (declaracion)</t>
+          <t>guion_45_60s</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>El simulacro está programado para el lunes 12 de octubre.</t>
+          <t>El primero señala que el Fondo Monetario Internacional proyecta un crecimiento cercano al cinco por ciento para el año 2026 [N-34877dd09e6b:titulo][N-34877dd09e6b:fecha].</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>[N-7f5a31e89279:titulo] "Bocas del Toro afina detalles para el III Simulacro de Evacuación este lunes 12 de octubre"</t>
+          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"
+[N-34877dd09e6b:fecha] "2026-10-07T22:00:00Z"</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="n"/>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>desarrolla la sigla FMI, que no está escrita así en lo citado</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -7506,30 +7492,35 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-c4339fd4cfad</t>
+          <t>CASO-EV-N-34877dd09e6b</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>afirmación (declaracion)</t>
+          <t>guion_45_60s</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>El proyecto modificado plantea 30% menos en compra de pañales, telefonía y otros beneficios para jubilados.</t>
+          <t>El segundo anuncia que un economista explicará cómo las tasas de interés podrían elevar las cuotas de los préstamos en el país [N-bc0c4a46f2c5:titulo][N-bc0c4a46f2c5:fecha].</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>[N-c4339fd4cfad:titulo] "Descuentos para jubilados: Proyecto modificado plantea 30% menos en compra de pañales, telefonía y otros beneficios"</t>
+          <t>[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"
+[N-bc0c4a46f2c5:fecha] "2026-10-08T13:23:50Z"</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n"/>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>el titular dice "explica"; la frase lo pasa a futuro ("explicará")</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -7537,30 +7528,35 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-1a8d986bf866</t>
+          <t>CASO-EV-N-34877dd09e6b</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>afirmación (declaracion)</t>
+          <t>copy_digital</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Explosión demográfica en Panamá Este aumenta la presión sobre el transporte público</t>
+          <t>TVN reporta que el FMI prevé un crecimiento del 5% para Panamá en 2026 y que un economista analizará el posible aumento de cuotas de préstamos por las tasas de interés [N-34877dd09e6b:titulo][N-bc0c4a46f2c5:titulo].</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>[N-1a8d986bf866:titulo] "Explosión demográfica en Panamá Este aumenta la presión sobre el transporte público"</t>
+          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"
+[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n"/>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>atribuye a TVN sin citar el campo medio y redondea "cerca de 5%" a "5%"</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -7568,7 +7564,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-e2e7ae51395c</t>
+          <t>CASO-EV-N-e7673d45b48a</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -7578,12 +7574,14 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>El ITSE se incorpora a una iniciativa que busca proyectar el café panameño y capacitar baristas.</t>
+          <t>Lau Cortés: Ordenan detención domiciliaria e imputan cargos por enriquecimiento injustificado y blanqueo de capitales</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>[N-e2e7ae51395c:titulo] "ITSE se suma a iniciativa para proyectar el café panameño y formar baristas"</t>
+          <t>[N-e7673d45b48a:titulo] "Lau Cortés: Ordenan detención domiciliaria e imputan cargos por enriquecimiento injustificado y blanqueo de capitales"
+[N-e7673d45b48a:medio] "TVN"
+[N-e7673d45b48a:fecha] "2026-10-08T02:30:00Z"</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -7599,7 +7597,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
+          <t>CASO-EV-N-5bf4576df900</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -7609,13 +7607,14 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TVN publicó un titular que indica que el FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026.</t>
+          <t>La Asamblea debatió la renovación del contrato de Ciudad del Saber, generando cuestionamientos por exoneraciones.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"
-[N-34877dd09e6b:medio] "TVN"</t>
+          <t>[N-5bf4576df900:titulo] "Asamblea: Debate por la renovación del contrato de Ciudad del Saber genera cuestionamientos por exoneraciones"
+[N-5bf4576df900:medio] "TVN"
+[N-5bf4576df900:fecha] "2026-10-08T01:14:47Z"</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -7624,338 +7623,10 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>afirmación (declaracion)</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TVN publicó un titular que pregunta si subirán las cuotas de préstamos y menciona que un economista explica el impacto de las tasas de interés en la economía panameña.</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"
-[N-bc0c4a46f2c5:medio] "TVN"</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TVN publicó un titular indicando que el FMI proyecta un crecimiento cercano al 5% para la economía de Panamá en 2026 [N-34877dd09e6b:titulo].</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>En otra publicación, el medio plantea la pregunta sobre si subirán las cuotas de préstamos, citando a un economista que explica el impacto de las tasas de interés [N-bc0c4a46f2c5:titulo].</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>guion_45_60s</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>El primero indica que el FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026 [N-34877dd09e6b:titulo].</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>guion_45_60s</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Esta información fue publicada por el medio el 7 de octubre de 2026 [N-34877dd09e6b:fecha].</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>[N-34877dd09e6b:fecha] "2026-10-07T22:00:00Z"</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>guion_45_60s</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>En una segunda nota, TVN pregunta si subirán las cuotas de préstamos, mencionando que un economista explica el impacto de las tasas de interés en la economía panameña [N-bc0c4a46f2c5:titulo].</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>guion_45_60s</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Esta publicación data del 8 de octubre de 2026 [N-bc0c4a46f2c5:fecha].</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>[N-bc0c4a46f2c5:fecha] "2026-10-08T13:23:50Z"</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-34877dd09e6b</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>copy_digital</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>TVN reporta que el FMI proyecta un crecimiento cercano al 5% para 2026 [N-34877dd09e6b:titulo] y debate el impacto de las tasas de interés en las cuotas de préstamos [N-bc0c4a46f2c5:titulo].</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>[N-34877dd09e6b:titulo] "FMI proyecta que la economía de Panamá crecerá cerca de 5% este 2026"
-[N-bc0c4a46f2c5:titulo] "¿Subirán las cuotas de préstamos? Economista explica el impacto de las tasas de interés en la economía panameña"</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-e7673d45b48a</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>afirmación (declaracion)</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TVN informa que se ordenó la detención domiciliaria e imputaron cargos a Lau Cortés por enriquecimiento injustificado y blanqueo de capitales.</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>[N-e7673d45b48a:titulo] "Lau Cortés: Ordenan detención domiciliaria e imputan cargos por enriquecimiento injustificado y blanqueo de capitales"</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>atribuye la nota a TVN sin citar el campo medio</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>CASO-EV-N-5bf4576df900</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>afirmación (declaracion)</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>El titular indica que la Asamblea está debatiendo la renovación del contrato de Ciudad del Saber y que existen cuestionamientos por exoneraciones.</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>[N-5bf4576df900:titulo] "Asamblea: Debate por la renovación del contrato de Ciudad del Saber genera cuestionamientos por exoneraciones"</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elija una opción del menú desplegable." type="list">
+    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elija una opción del menú desplegable." type="list">
       <formula1>"si,parcial,no"</formula1>
     </dataValidation>
   </dataValidations>
